--- a/src/episodes/episode-04/scripts.xlsx
+++ b/src/episodes/episode-04/scripts.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>镜头</t>
   </si>
@@ -44,6 +44,15 @@
   </si>
   <si>
     <t>镜头脚本</t>
+  </si>
+  <si>
+    <t>真人出镜</t>
+  </si>
+  <si>
+    <t>你今天焦虑的事情，不过是小学3年级时候，忘戴的红领巾。</t>
+  </si>
+  <si>
+    <t>真人</t>
   </si>
 </sst>
 </file>
@@ -659,7 +668,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -667,6 +676,12 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1202,8 +1217,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D1"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:D2"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" spans="1:4">
       <c r="A1" s="1" t="s">
@@ -1219,6 +1234,20 @@
         <v>3</v>
       </c>
     </row>
+    <row r="2" ht="98" spans="1:4">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>3</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/src/episodes/episode-04/scripts.xlsx
+++ b/src/episodes/episode-04/scripts.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
   <si>
     <t>镜头</t>
   </si>
@@ -53,6 +53,12 @@
   </si>
   <si>
     <t>真人</t>
+  </si>
+  <si>
+    <t>小学的时候，学校要求学生要佩戴红领巾</t>
+  </si>
+  <si>
+    <t>有一次，我忘记戴红领巾。被要求在教室门外罚站。</t>
   </si>
 </sst>
 </file>
@@ -668,12 +674,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1217,20 +1226,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="1" outlineLevelCol="3"/>
+  <dimension ref="A1:D4"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <cols>
+    <col min="2" max="2" width="9.81818181818182" style="2"/>
+    <col min="3" max="3" width="46.1818181818182" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" s="1" customFormat="1" ht="28" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="3" t="s">
         <v>3</v>
       </c>
     </row>
@@ -1238,14 +1251,30 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="5" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="4" ht="28" spans="1:4">
+      <c r="B4" s="2">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/src/episodes/episode-04/scripts.xlsx
+++ b/src/episodes/episode-04/scripts.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>镜头</t>
   </si>
@@ -58,7 +58,16 @@
     <t>小学的时候，学校要求学生要佩戴红领巾</t>
   </si>
   <si>
-    <t>有一次，我忘记戴红领巾。被要求在教室门外罚站。</t>
+    <t>有一次，我忘记戴红领巾，被老师当着全班的面批评。</t>
+  </si>
+  <si>
+    <t>又被要求在教室门外罚站</t>
+  </si>
+  <si>
+    <t>多年之后，我回想起来。发现那不过只是一个微不足道的错误，对人生没有丝毫影响。</t>
+  </si>
+  <si>
+    <t>今天，让你焦虑的一切事情，不过都只是小学3年级时候你忘戴的红领巾而已。</t>
   </si>
 </sst>
 </file>
@@ -1226,8 +1235,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="3" outlineLevelCol="3"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14" outlineLevelRow="6" outlineLevelCol="3"/>
   <cols>
     <col min="2" max="2" width="9.81818181818182" style="2"/>
     <col min="3" max="3" width="46.1818181818182" customWidth="1"/>
@@ -1277,6 +1286,30 @@
         <v>8</v>
       </c>
     </row>
+    <row r="5" spans="1:4">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" ht="28" spans="1:4">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" ht="28" spans="1:4">
+      <c r="B7" s="2">
+        <v>3</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
